--- a/results_combat/solution_thrifty.xlsx
+++ b/results_combat/solution_thrifty.xlsx
@@ -26284,7 +26284,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="116">
@@ -28341,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>100</v>
+        <v>42.1658</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -30313,7 +30313,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>65.9513</v>
+        <v>65.4513</v>
       </c>
       <c r="H259" t="n">
         <v>34.0487</v>
@@ -30957,7 +30957,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>61.3674</v>
+        <v>60.8674</v>
       </c>
       <c r="H282" t="n">
         <v>38.6326</v>

--- a/results_combat/solution_thrifty.xlsx
+++ b/results_combat/solution_thrifty.xlsx
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.148</v>
+        <v>5.1479</v>
       </c>
     </row>
     <row r="12">
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4098</v>
+        <v>5.4097</v>
       </c>
     </row>
     <row r="13">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5623</v>
+        <v>3.5622</v>
       </c>
     </row>
     <row r="41">
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.0743</v>
+        <v>5.0742</v>
       </c>
     </row>
     <row r="46">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>5.0477</v>
+        <v>5.0476</v>
       </c>
     </row>
     <row r="57">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>7.174</v>
+        <v>7.1739</v>
       </c>
     </row>
     <row r="60">
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.9156</v>
+        <v>3.9155</v>
       </c>
     </row>
     <row r="70">
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>48.9178</v>
+        <v>48.9177</v>
       </c>
     </row>
     <row r="77">
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>10.9553</v>
+        <v>10.9552</v>
       </c>
     </row>
     <row r="82">
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>11.4638</v>
+        <v>11.4637</v>
       </c>
     </row>
     <row r="83">
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>3.9385</v>
+        <v>3.9384</v>
       </c>
     </row>
     <row r="85">
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>12.6018</v>
+        <v>12.6017</v>
       </c>
     </row>
     <row r="95">
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>9.246600000000001</v>
+        <v>9.246499999999999</v>
       </c>
     </row>
     <row r="96">
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>4.7228</v>
+        <v>4.7227</v>
       </c>
     </row>
     <row r="98">
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>8.783200000000001</v>
+        <v>8.783099999999999</v>
       </c>
     </row>
     <row r="110">
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>6.4124</v>
+        <v>6.4123</v>
       </c>
     </row>
     <row r="111">
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>16.416</v>
+        <v>16.4159</v>
       </c>
     </row>
     <row r="120">
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>7.6653</v>
+        <v>7.6652</v>
       </c>
     </row>
     <row r="132">
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>5.1602</v>
+        <v>5.1601</v>
       </c>
     </row>
     <row r="133">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>4.9633</v>
+        <v>4.9632</v>
       </c>
     </row>
     <row r="181">
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>3.5473</v>
+        <v>3.5472</v>
       </c>
     </row>
     <row r="183">
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>2.8499</v>
+        <v>2.8498</v>
       </c>
     </row>
     <row r="197">
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>13.4865</v>
+        <v>13.4864</v>
       </c>
     </row>
     <row r="207">
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>5.1339</v>
+        <v>5.1338</v>
       </c>
     </row>
     <row r="214">
@@ -6427,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>4.7803</v>
+        <v>4.7802</v>
       </c>
     </row>
     <row r="215">
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>25.6255</v>
+        <v>25.6254</v>
       </c>
     </row>
     <row r="218">
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>17.3573</v>
+        <v>17.3572</v>
       </c>
     </row>
     <row r="219">
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>37.8966</v>
+        <v>37.8965</v>
       </c>
     </row>
     <row r="249">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>18.5607</v>
+        <v>18.5606</v>
       </c>
     </row>
     <row r="250">
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>34.3076</v>
+        <v>34.3075</v>
       </c>
     </row>
     <row r="259">
@@ -7687,7 +7687,7 @@
         <v>10</v>
       </c>
       <c r="H259" t="n">
-        <v>34.4916</v>
+        <v>34.4915</v>
       </c>
     </row>
     <row r="260">
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>10.8914</v>
+        <v>10.8913</v>
       </c>
     </row>
     <row r="269">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>7.2198</v>
+        <v>7.2197</v>
       </c>
     </row>
     <row r="295">
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>5.5018</v>
+        <v>5.5017</v>
       </c>
     </row>
     <row r="303">
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>19.6821</v>
+        <v>19.682</v>
       </c>
     </row>
     <row r="316">
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>5.0652</v>
+        <v>5.0651</v>
       </c>
     </row>
     <row r="318">
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>40.0724</v>
+        <v>40.0723</v>
       </c>
     </row>
     <row r="322">
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>4.6767</v>
+        <v>4.6766</v>
       </c>
     </row>
     <row r="330">
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>6.7187</v>
+        <v>6.7186</v>
       </c>
     </row>
     <row r="346">
@@ -10515,7 +10515,7 @@
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>36.4346</v>
+        <v>36.4345</v>
       </c>
     </row>
     <row r="361">
@@ -10655,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>8.4171</v>
+        <v>8.417</v>
       </c>
     </row>
     <row r="366">
@@ -10767,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="H369" t="n">
-        <v>3.7808</v>
+        <v>3.7807</v>
       </c>
     </row>
     <row r="370">
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>9.0792</v>
+        <v>9.0791</v>
       </c>
     </row>
     <row r="373">
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="H380" t="n">
-        <v>7.8034</v>
+        <v>7.8033</v>
       </c>
     </row>
     <row r="381">
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>35.8541</v>
+        <v>35.854</v>
       </c>
     </row>
     <row r="382">
@@ -11131,7 +11131,7 @@
         <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>48.2246</v>
+        <v>48.2245</v>
       </c>
     </row>
     <row r="383">
@@ -11243,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>15.5779</v>
+        <v>15.5778</v>
       </c>
     </row>
     <row r="387">
@@ -11551,7 +11551,7 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>4.0087</v>
+        <v>4.0086</v>
       </c>
     </row>
     <row r="398">
@@ -11663,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>15.8875</v>
+        <v>15.8874</v>
       </c>
     </row>
     <row r="402">
@@ -11831,7 +11831,7 @@
         <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>26.3258</v>
+        <v>26.3257</v>
       </c>
     </row>
     <row r="408">
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>4.0147</v>
+        <v>4.0146</v>
       </c>
     </row>
     <row r="410">
@@ -11943,7 +11943,7 @@
         <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>7.5799</v>
+        <v>7.5798</v>
       </c>
     </row>
     <row r="412">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="H412" t="n">
-        <v>3.4854</v>
+        <v>3.4853</v>
       </c>
     </row>
     <row r="413">
@@ -11999,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="H413" t="n">
-        <v>9.097099999999999</v>
+        <v>9.097</v>
       </c>
     </row>
     <row r="414">
@@ -12363,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>8.323700000000001</v>
+        <v>8.323600000000001</v>
       </c>
     </row>
     <row r="427">
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>4.3786</v>
+        <v>4.3785</v>
       </c>
     </row>
     <row r="428">
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="H436" t="n">
-        <v>3.3896</v>
+        <v>3.3895</v>
       </c>
     </row>
     <row r="437">
@@ -12671,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="H437" t="n">
-        <v>3.3333</v>
+        <v>3.3332</v>
       </c>
     </row>
     <row r="438">
@@ -12755,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>5.0945</v>
+        <v>5.0944</v>
       </c>
     </row>
     <row r="441">
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="H445" t="n">
-        <v>3.6167</v>
+        <v>3.6166</v>
       </c>
     </row>
     <row r="446">
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
       <c r="H472" t="n">
-        <v>14.6171</v>
+        <v>14.617</v>
       </c>
     </row>
     <row r="473">
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="H479" t="n">
-        <v>6.2362</v>
+        <v>6.2361</v>
       </c>
     </row>
     <row r="480">
@@ -14155,7 +14155,7 @@
         <v>0</v>
       </c>
       <c r="H490" t="n">
-        <v>3.6008</v>
+        <v>3.6007</v>
       </c>
     </row>
     <row r="491">
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="H493" t="n">
-        <v>7.1331</v>
+        <v>7.133</v>
       </c>
     </row>
     <row r="494">
@@ -14323,7 +14323,7 @@
         <v>0</v>
       </c>
       <c r="H496" t="n">
-        <v>3.7871</v>
+        <v>3.787</v>
       </c>
     </row>
     <row r="497">
@@ -15163,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="H526" t="n">
-        <v>4.7164</v>
+        <v>4.7163</v>
       </c>
     </row>
     <row r="527">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="H527" t="n">
-        <v>9.2506</v>
+        <v>9.250500000000001</v>
       </c>
     </row>
     <row r="528">
@@ -15387,7 +15387,7 @@
         <v>0</v>
       </c>
       <c r="H534" t="n">
-        <v>3.5461</v>
+        <v>3.546</v>
       </c>
     </row>
     <row r="535">
@@ -15527,7 +15527,7 @@
         <v>0</v>
       </c>
       <c r="H539" t="n">
-        <v>4.5537</v>
+        <v>4.5536</v>
       </c>
     </row>
     <row r="540">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>45.5446</v>
+        <v>45.5445</v>
       </c>
     </row>
     <row r="13">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>45.2555</v>
+        <v>45.2554</v>
       </c>
     </row>
     <row r="16">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>89.0411</v>
+        <v>89.041</v>
       </c>
     </row>
     <row r="31">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>93.7107</v>
+        <v>93.7106</v>
       </c>
     </row>
     <row r="32">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>30.3887</v>
+        <v>30.3886</v>
       </c>
     </row>
     <row r="46">
@@ -24436,7 +24436,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>62.6437</v>
+        <v>62.6436</v>
       </c>
     </row>
     <row r="50">
@@ -24632,7 +24632,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>55.5556</v>
+        <v>55.5555</v>
       </c>
     </row>
     <row r="57">
@@ -24716,7 +24716,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>34.3662</v>
+        <v>34.3661</v>
       </c>
     </row>
     <row r="60">
@@ -24828,7 +24828,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>84.5865</v>
+        <v>84.5864</v>
       </c>
     </row>
     <row r="64">
@@ -24996,7 +24996,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>54.0984</v>
+        <v>54.0983</v>
       </c>
     </row>
     <row r="70">
@@ -25192,7 +25192,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>79.76990000000001</v>
+        <v>79.7698</v>
       </c>
     </row>
     <row r="77">
@@ -25332,7 +25332,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>55.1929</v>
+        <v>55.1928</v>
       </c>
     </row>
     <row r="82">
@@ -25360,7 +25360,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>42.2078</v>
+        <v>42.2077</v>
       </c>
     </row>
     <row r="83">
@@ -25668,7 +25668,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>83.9117</v>
+        <v>83.91160000000001</v>
       </c>
     </row>
     <row r="94">
@@ -25696,7 +25696,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>47.1366</v>
+        <v>47.1365</v>
       </c>
     </row>
     <row r="95">
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>32.8829</v>
+        <v>32.8828</v>
       </c>
     </row>
     <row r="97">
@@ -25780,7 +25780,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>33.7553</v>
+        <v>33.7552</v>
       </c>
     </row>
     <row r="98">
@@ -26088,7 +26088,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>43.1953</v>
+        <v>43.1952</v>
       </c>
     </row>
     <row r="109">
@@ -26116,7 +26116,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>56.4394</v>
+        <v>56.4393</v>
       </c>
     </row>
     <row r="110">
@@ -26144,7 +26144,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>38.6525</v>
+        <v>38.6524</v>
       </c>
     </row>
     <row r="111">
@@ -26396,7 +26396,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>53.9652</v>
+        <v>53.9651</v>
       </c>
     </row>
     <row r="120">
@@ -26452,7 +26452,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>29.8137</v>
+        <v>29.8136</v>
       </c>
     </row>
     <row r="122">
@@ -26760,7 +26760,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>58</v>
+        <v>57.9999</v>
       </c>
     </row>
     <row r="133">
@@ -27180,7 +27180,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>35.4244</v>
+        <v>35.4243</v>
       </c>
     </row>
     <row r="148">
@@ -27348,7 +27348,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>40.2685</v>
+        <v>40.2684</v>
       </c>
     </row>
     <row r="154">
@@ -27513,7 +27513,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>59.7734</v>
+        <v>59.7733</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -28341,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>42.1658</v>
+        <v>42.1657</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -28661,7 +28661,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>33.3876</v>
+        <v>33.3875</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -28720,7 +28720,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>45.8065</v>
+        <v>45.8064</v>
       </c>
     </row>
     <row r="203">
@@ -28776,7 +28776,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>81.6794</v>
+        <v>81.6793</v>
       </c>
     </row>
     <row r="205">
@@ -29000,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>72.41379999999999</v>
+        <v>72.41370000000001</v>
       </c>
     </row>
     <row r="213">
@@ -29084,7 +29084,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>50.4505</v>
+        <v>50.4504</v>
       </c>
     </row>
     <row r="216">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>60.0551</v>
+        <v>60.055</v>
       </c>
     </row>
     <row r="218">
@@ -29168,7 +29168,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>56.8401</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="219">
@@ -29196,7 +29196,7 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>34.8315</v>
+        <v>34.8314</v>
       </c>
     </row>
     <row r="220">
@@ -29504,7 +29504,7 @@
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>52.1277</v>
+        <v>52.1276</v>
       </c>
     </row>
     <row r="231">
@@ -30008,7 +30008,7 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>43.0287</v>
+        <v>43.0286</v>
       </c>
     </row>
     <row r="249">
@@ -30288,7 +30288,7 @@
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>41.5068</v>
+        <v>41.5067</v>
       </c>
     </row>
     <row r="259">
@@ -30313,7 +30313,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>65.4513</v>
+        <v>65.4512</v>
       </c>
       <c r="H259" t="n">
         <v>34.0487</v>
@@ -30596,7 +30596,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>55.4645</v>
+        <v>55.4644</v>
       </c>
     </row>
     <row r="270">
@@ -30957,7 +30957,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>60.8674</v>
+        <v>60.8673</v>
       </c>
       <c r="H282" t="n">
         <v>38.6326</v>
@@ -31520,7 +31520,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>80.86960000000001</v>
+        <v>80.8695</v>
       </c>
     </row>
     <row r="303">
@@ -31548,7 +31548,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>91.1765</v>
+        <v>91.1764</v>
       </c>
     </row>
     <row r="304">
@@ -31576,7 +31576,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>94.68089999999999</v>
+        <v>94.6808</v>
       </c>
     </row>
     <row r="305">
@@ -31940,7 +31940,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>41.7476</v>
+        <v>41.7475</v>
       </c>
     </row>
     <row r="318">
@@ -32052,7 +32052,7 @@
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>37.3699</v>
+        <v>37.3698</v>
       </c>
     </row>
     <row r="322">
@@ -32752,7 +32752,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>32.948</v>
+        <v>32.9479</v>
       </c>
     </row>
     <row r="347">
@@ -33144,7 +33144,7 @@
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>42.7292</v>
+        <v>42.7291</v>
       </c>
     </row>
     <row r="361">
@@ -33228,7 +33228,7 @@
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>40.3509</v>
+        <v>40.3508</v>
       </c>
     </row>
     <row r="364">
@@ -33284,7 +33284,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>64.7059</v>
+        <v>64.7058</v>
       </c>
     </row>
     <row r="366">
@@ -33340,7 +33340,7 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>42.9719</v>
+        <v>42.9718</v>
       </c>
     </row>
     <row r="368">
@@ -33480,7 +33480,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>80.6283</v>
+        <v>80.62820000000001</v>
       </c>
     </row>
     <row r="373">
@@ -33508,7 +33508,7 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>41.3889</v>
+        <v>41.3888</v>
       </c>
     </row>
     <row r="374">
@@ -33732,7 +33732,7 @@
         <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>49.2333</v>
+        <v>49.2332</v>
       </c>
     </row>
     <row r="382">
@@ -33760,7 +33760,7 @@
         <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>38.6353</v>
+        <v>38.6352</v>
       </c>
     </row>
     <row r="383">
@@ -34460,7 +34460,7 @@
         <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>57.732</v>
+        <v>57.7319</v>
       </c>
     </row>
     <row r="408">
@@ -34516,7 +34516,7 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>80.9524</v>
+        <v>80.95229999999999</v>
       </c>
     </row>
     <row r="410">
@@ -34572,7 +34572,7 @@
         <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>29.5195</v>
+        <v>29.5194</v>
       </c>
     </row>
     <row r="412">
@@ -34992,7 +34992,7 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>98.6014</v>
+        <v>98.60129999999999</v>
       </c>
     </row>
     <row r="427">
@@ -35020,7 +35020,7 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>44.8485</v>
+        <v>44.8484</v>
       </c>
     </row>
     <row r="428">
@@ -35272,7 +35272,7 @@
         <v>0</v>
       </c>
       <c r="H436" t="n">
-        <v>57.5758</v>
+        <v>57.5757</v>
       </c>
     </row>
     <row r="437">
@@ -35300,7 +35300,7 @@
         <v>0</v>
       </c>
       <c r="H437" t="n">
-        <v>60.8696</v>
+        <v>60.8695</v>
       </c>
     </row>
     <row r="438">
@@ -35384,7 +35384,7 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>60.1399</v>
+        <v>60.1398</v>
       </c>
     </row>
     <row r="441">
@@ -35468,7 +35468,7 @@
         <v>0</v>
       </c>
       <c r="H443" t="n">
-        <v>44.6809</v>
+        <v>44.6808</v>
       </c>
     </row>
     <row r="444">
@@ -35720,7 +35720,7 @@
         <v>0</v>
       </c>
       <c r="H452" t="n">
-        <v>45.8537</v>
+        <v>45.8536</v>
       </c>
     </row>
     <row r="453">
@@ -36000,7 +36000,7 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>26.1981</v>
+        <v>26.198</v>
       </c>
     </row>
     <row r="463">
@@ -36196,7 +36196,7 @@
         <v>0</v>
       </c>
       <c r="H469" t="n">
-        <v>94.2029</v>
+        <v>94.2028</v>
       </c>
     </row>
     <row r="470">
@@ -36476,7 +36476,7 @@
         <v>0</v>
       </c>
       <c r="H479" t="n">
-        <v>38.5455</v>
+        <v>38.5454</v>
       </c>
     </row>
     <row r="480">
@@ -36784,7 +36784,7 @@
         <v>0</v>
       </c>
       <c r="H490" t="n">
-        <v>42.069</v>
+        <v>42.0689</v>
       </c>
     </row>
     <row r="491">
@@ -36868,7 +36868,7 @@
         <v>0</v>
       </c>
       <c r="H493" t="n">
-        <v>62.0513</v>
+        <v>62.0512</v>
       </c>
     </row>
     <row r="494">
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="H496" t="n">
-        <v>48.855</v>
+        <v>48.8549</v>
       </c>
     </row>
     <row r="497">
@@ -37120,7 +37120,7 @@
         <v>0</v>
       </c>
       <c r="H502" t="n">
-        <v>37.8049</v>
+        <v>37.8048</v>
       </c>
     </row>
     <row r="503">
@@ -37792,7 +37792,7 @@
         <v>0</v>
       </c>
       <c r="H526" t="n">
-        <v>41.6667</v>
+        <v>41.6666</v>
       </c>
     </row>
     <row r="527">
@@ -37904,7 +37904,7 @@
         <v>0</v>
       </c>
       <c r="H530" t="n">
-        <v>35.533</v>
+        <v>35.5329</v>
       </c>
     </row>
     <row r="531">
@@ -37988,7 +37988,7 @@
         <v>0</v>
       </c>
       <c r="H533" t="n">
-        <v>46.7662</v>
+        <v>46.7661</v>
       </c>
     </row>
     <row r="534">
